--- a/TestCases/Specialty_TestCase.xlsx
+++ b/TestCases/Specialty_TestCase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnNganh\SpringMediCareWeb-Selenium-Testing\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F466B3-895E-44EC-820E-2BF274E52C2C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A9645B-1895-4604-B69F-C2FF0E3906C0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -173,13 +173,6 @@
     <t>Kiểm tra nút Xem chi tiết khoa hiển thị đúng thông tin chuyên khoa được chọn</t>
   </si>
   <si>
-    <t>1: Patient mở trang Chuyên khoa.
-2: Chọn chuyên khoa mắt.
-3: Nhấn Xem chi tiết khoa.
-4: Quan sát trang/kết quả được hiển thị.
-5: Kiểm tra bác sĩ hiển thị có thuộc chuyên khoa.</t>
-  </si>
-  <si>
     <t>Hệ thống hiển thị hoặc điều hướng đến phần chi tiết của đúng chuyên khoa Mắt. Tên chuyên khoa và nội dung chi tiết tương ứng với chuyên khoa đã chọn. Không hiển thị nhầm chuyên khoa và không phát sinh lỗi.</t>
   </si>
   <si>
@@ -188,13 +181,20 @@
   <si>
     <t>Hiển thị đúng và đầy đủ thông tin chi tiết của chuyên khoa được chọn.</t>
   </si>
+  <si>
+    <t>1: Patient mở trang Chuyên khoa.
+2: Chọn chuyên khoa mắt.
+3: Nhấn Xem chi tiết khoa.
+4: Quan sát trang/kết quả được hiển thị.
+5: Kiểm tra tên chuyên khoa, thông tin giới thiệu, số lượng bác sĩ và đội ngũ bác sĩ trực thuộc hiển thị đúng với chuyên khoa Mắt.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="d\-m"/>
+    <numFmt numFmtId="164" formatCode="d\-m"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -439,37 +439,37 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -709,9 +709,9 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -735,9 +735,9 @@
     </row>
     <row r="2" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -763,11 +763,11 @@
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="27"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -793,11 +793,11 @@
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="22"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="27"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -823,11 +823,11 @@
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="22"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="27"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -944,30 +944,30 @@
       <c r="X8" s="3"/>
     </row>
     <row r="9" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="29" t="s">
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="32" t="s">
+      <c r="I9" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="32" t="s">
+      <c r="J9" s="30" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="3"/>
@@ -986,16 +986,16 @@
       <c r="X9" s="3"/>
     </row>
     <row r="10" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -1013,15 +1013,15 @@
     </row>
     <row r="11" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="22"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="27"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -1047,11 +1047,11 @@
       <c r="C12" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
       <c r="G12" s="17" t="s">
         <v>23</v>
       </c>
@@ -1089,11 +1089,11 @@
       <c r="C13" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
       <c r="G13" s="17" t="s">
         <v>29</v>
       </c>
@@ -1131,11 +1131,11 @@
       <c r="C14" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
       <c r="G14" s="17" t="s">
         <v>35</v>
       </c>
@@ -1173,11 +1173,11 @@
       <c r="C15" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="33" t="s">
+      <c r="D15" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
       <c r="G15" s="17" t="s">
         <v>41</v>
       </c>
@@ -1213,15 +1213,15 @@
         <v>44</v>
       </c>
       <c r="C16" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="17" t="s">
         <v>46</v>
-      </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="17" t="s">
-        <v>47</v>
       </c>
       <c r="H16" s="18">
         <v>46252</v>
@@ -1230,7 +1230,7 @@
         <v>5</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
@@ -26287,6 +26287,13 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="D9:F10"/>
@@ -26298,13 +26305,6 @@
     <mergeCell ref="I9:I10"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="D14:F14"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G12" r:id="rId1" xr:uid="{00000000-0004-0000-0D00-000000000000}"/>

--- a/TestCases/Specialty_TestCase.xlsx
+++ b/TestCases/Specialty_TestCase.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnNganh\SpringMediCareWeb-Selenium-Testing\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A9645B-1895-4604-B69F-C2FF0E3906C0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5075D86A-2A7F-40FA-82E2-D20FB1F626F3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12792" windowHeight="6960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="SPECIALTY" sheetId="14" r:id="rId1"/>
+    <sheet name="SPECIALTY" sheetId="15" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="ACTION">#REF!</definedName>
@@ -76,10 +76,10 @@
     <t>Note</t>
   </si>
   <si>
-    <t>SPECIALTY400 - Specialty Management</t>
+    <t>SPECIALTY - Specialty Management</t>
   </si>
   <si>
-    <t>SPECIALTY1 - View and Search Specialties</t>
+    <t>Specialty Information</t>
   </si>
   <si>
     <t>TC-SPECIALTY-001</t>
@@ -173,6 +173,13 @@
     <t>Kiểm tra nút Xem chi tiết khoa hiển thị đúng thông tin chuyên khoa được chọn</t>
   </si>
   <si>
+    <t>1: Patient mở trang Chuyên khoa.
+2: Chọn chuyên khoa mắt.
+3: Nhấn Xem chi tiết khoa.
+4: Quan sát trang/kết quả được hiển thị.
+5: Kiểm tra tên chuyên khoa, thông tin giới thiệu, số lượng bác sĩ và đội ngũ bác sĩ trực thuộc hiển thị đúng với chuyên khoa Mắt.</t>
+  </si>
+  <si>
     <t>Hệ thống hiển thị hoặc điều hướng đến phần chi tiết của đúng chuyên khoa Mắt. Tên chuyên khoa và nội dung chi tiết tương ứng với chuyên khoa đã chọn. Không hiển thị nhầm chuyên khoa và không phát sinh lỗi.</t>
   </si>
   <si>
@@ -181,20 +188,13 @@
   <si>
     <t>Hiển thị đúng và đầy đủ thông tin chi tiết của chuyên khoa được chọn.</t>
   </si>
-  <si>
-    <t>1: Patient mở trang Chuyên khoa.
-2: Chọn chuyên khoa mắt.
-3: Nhấn Xem chi tiết khoa.
-4: Quan sát trang/kết quả được hiển thị.
-5: Kiểm tra tên chuyên khoa, thông tin giới thiệu, số lượng bác sĩ và đội ngũ bác sĩ trực thuộc hiển thị đúng với chuyên khoa Mắt.</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="d\-m"/>
+    <numFmt numFmtId="165" formatCode="d\-m"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -439,37 +439,37 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -688,7 +688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -709,9 +709,9 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -735,9 +735,9 @@
     </row>
     <row r="2" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -763,11 +763,11 @@
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="27"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="25"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -793,11 +793,11 @@
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="27"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="25"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -823,11 +823,11 @@
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="27"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="25"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -944,30 +944,30 @@
       <c r="X8" s="3"/>
     </row>
     <row r="9" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="28" t="s">
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="30" t="s">
+      <c r="H9" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="30" t="s">
+      <c r="I9" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="30" t="s">
+      <c r="J9" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="3"/>
@@ -986,16 +986,16 @@
       <c r="X9" s="3"/>
     </row>
     <row r="10" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="29"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -1013,15 +1013,15 @@
     </row>
     <row r="11" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="27"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="25"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -1047,11 +1047,11 @@
       <c r="C12" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
       <c r="G12" s="17" t="s">
         <v>23</v>
       </c>
@@ -1089,11 +1089,11 @@
       <c r="C13" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
       <c r="G13" s="17" t="s">
         <v>29</v>
       </c>
@@ -1131,11 +1131,11 @@
       <c r="C14" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
       <c r="G14" s="17" t="s">
         <v>35</v>
       </c>
@@ -1173,11 +1173,11 @@
       <c r="C15" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
       <c r="G15" s="17" t="s">
         <v>41</v>
       </c>
@@ -1213,15 +1213,15 @@
         <v>44</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
+      <c r="D16" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
       <c r="G16" s="17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H16" s="18">
         <v>46252</v>
@@ -1230,7 +1230,7 @@
         <v>5</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
@@ -26287,6 +26287,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D9:F10"/>
+    <mergeCell ref="D12:F12"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B4:D4"/>
@@ -26294,24 +26305,13 @@
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D9:F10"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="D14:F14"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G12" r:id="rId1" xr:uid="{00000000-0004-0000-0D00-000000000000}"/>
-    <hyperlink ref="G13" r:id="rId2" xr:uid="{00000000-0004-0000-0D00-000001000000}"/>
-    <hyperlink ref="G14" r:id="rId3" xr:uid="{00000000-0004-0000-0D00-000002000000}"/>
-    <hyperlink ref="G15" r:id="rId4" xr:uid="{00000000-0004-0000-0D00-000003000000}"/>
-    <hyperlink ref="G16" r:id="rId5" xr:uid="{00000000-0004-0000-0D00-000004000000}"/>
+    <hyperlink ref="G12" r:id="rId1" xr:uid="{00000000-0004-0000-0E00-000000000000}"/>
+    <hyperlink ref="G13" r:id="rId2" xr:uid="{00000000-0004-0000-0E00-000001000000}"/>
+    <hyperlink ref="G14" r:id="rId3" xr:uid="{00000000-0004-0000-0E00-000002000000}"/>
+    <hyperlink ref="G15" r:id="rId4" xr:uid="{00000000-0004-0000-0E00-000003000000}"/>
+    <hyperlink ref="G16" r:id="rId5" xr:uid="{00000000-0004-0000-0E00-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
